--- a/DePara_Produtos_modelo.xlsx
+++ b/DePara_Produtos_modelo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SYSTANE UL; SYSTANE ULTRA (ALC)</t>
+          <t>SYSTANE UL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -454,12 +454,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SYSTANE COMPLETE</t>
+          <t>SYSTANE ULTRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SYSTANE COMP; SYSTANE COMPLETE (ALC)</t>
+          <t>SYSTANE UL (SLC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -471,12 +471,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PATANOL S</t>
+          <t>SYSTANE ULTRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PATANOL S (NVR); PATANOL S</t>
+          <t>SYSTANE U</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -488,12 +488,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CLARIL</t>
+          <t>SYSTANE COMPLETE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CLARIL (ALC)</t>
+          <t>SYSTANE COMP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -505,12 +505,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PATADAY</t>
+          <t>SYSTANE COMPLETE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PATADAY (NVR); PATADAY</t>
+          <t>SYSTANE COMPLETE (ALC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -522,12 +522,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MAXIDEX</t>
+          <t>PATANOL S</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MAXIDEX (NOVARTIS); MAXIDEX (ALC)</t>
+          <t>PATANOL S (NVR)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -539,12 +539,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TOBRADEX</t>
+          <t>PATANOL S</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOBRADEX (ALC)</t>
+          <t>PATANOL S</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -556,12 +556,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRED FORTE</t>
+          <t>CLARIL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PRED FORTE (ALC)</t>
+          <t>CLARIL (ALC)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -573,12 +573,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TRAVATAN Z</t>
+          <t>PATADAY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TRAVATAN Z (ALC); TRAVATAN</t>
+          <t>PATADAY (NVR)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -590,12 +590,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TOTAL 30</t>
+          <t>PATADAY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOTAL 30 (ALC)</t>
+          <t>PATADAY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -607,41 +607,177 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>MAXIDEX</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MAXIDEX (NOVARTIS)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MAXIDEX</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MAXIDEX (ALC)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TOBRADEX</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TOBRADEX (ALC)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PRED FORTE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PRED FORTE (ALC)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TRAVATAN Z</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TRAVATAN Z (ALC)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TRAVATAN Z</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TRAVATAN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TOTAL 30</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TOTAL 30 (ALC)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>DAILIES TOTAL1</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DAILIES TOTAL1 (ALC); DAILIES TOTAL ONE</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DAILIES TOTAL1 (ALC)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DAILIES TOTAL1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DAILIES TOTAL ONE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
         <is>
           <t>SYSTANE BALANCE</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>NAO</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
         <is>
           <t>REFRESH OPTIVE</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>NAO</t>
         </is>
@@ -658,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,7 +829,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nome do produto no sell-out. Múltiplos nomes separados por ; (ponto-e-vírgula)</t>
+          <t>Nome do produto no sell-out (UM nome por linha)</t>
         </is>
       </c>
     </row>
@@ -705,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM = mostra no dashboard. NAO = ignora (concorrentes, ruído, etc)</t>
+          <t>SIM = mostra no dashboard. NAO = ignora (concorrentes, ruído)</t>
         </is>
       </c>
     </row>
@@ -725,7 +861,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1. Use match EXATO no nome - sem fuzzy</t>
+          <t>1. UMA LINHA POR PAR sell-in/sell-out</t>
         </is>
       </c>
     </row>
@@ -733,7 +869,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2. Múltiplos nomes sell-out apontam pro MESMO sell-in (vão ser somados)</t>
+          <t>2. Para mapear MULTIPLOS nomes do sell-out pro MESMO sell-in,</t>
         </is>
       </c>
     </row>
@@ -741,7 +877,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3. PRODUTO_SELLIN vazio + INCLUIR_DASHBOARD=NAO = ignora completamente</t>
+          <t xml:space="preserve">   crie várias linhas com o mesmo PRODUTO_SELLIN</t>
         </is>
       </c>
     </row>
@@ -749,59 +885,147 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4. Produtos não listados aqui aparecem em produtos_nao_mapeados.csv</t>
+          <t>3. Match EXATO no nome (sem fuzzy)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4. Produtos não listados aparecem em produtos_nao_mapeados.csv</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>FLUXO:</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1. Roda script Python</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EXEMPLO:</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2. Vê no console quais produtos faltam mapear</t>
+          <t>Para o sell-in 'SYSTANE ULTRA' que aparece em 3 nomes diferentes no sell-out:</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PRODUTO_SELLIN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PRODUTO_SELLOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SYSTANE ULTRA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SYSTANE UL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SYSTANE ULTRA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SYSTANE UL (SLC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SYSTANE ULTRA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SYSTANE U</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>↑ As 3 linhas vão somar no mesmo SYSTANE ULTRA do dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FLUXO:</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1. Roda script Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2. Vê no console quais produtos faltam mapear</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
         <is>
           <t>3. Abre produtos_nao_mapeados.csv</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>4. Copia pra esta planilha e classifica</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5. Roda Python de novo - dashboard agora 100% mapeado</t>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4. Copia pra esta planilha (1 linha por par)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5. Roda Python de novo - dashboard 100% mapeado</t>
         </is>
       </c>
     </row>

--- a/DePara_Produtos_modelo.xlsx
+++ b/DePara_Produtos_modelo.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,12 +437,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SYSTANE ULTRA</t>
+          <t>AOHG MULTIFOCAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SYSTANE UL</t>
+          <t>AOHG MULTIFOCAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -454,12 +454,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SYSTANE ULTRA</t>
+          <t>PRECISION 1 TORIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SYSTANE UL (SLC)</t>
+          <t>PRECISION 1 TORIC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -471,12 +471,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SYSTANE ULTRA</t>
+          <t>AOHG TORIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SYSTANE U</t>
+          <t>AOHG TORIC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -488,12 +488,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SYSTANE COMPLETE</t>
+          <t>AOHG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SYSTANE COMP</t>
+          <t>AOHG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -505,12 +505,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SYSTANE COMPLETE</t>
+          <t>PRECISION 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SYSTANE COMPLETE (ALC)</t>
+          <t>PRECISION 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -522,12 +522,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PATANOL S</t>
+          <t>DAILIES TOTAL 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PATANOL S (NVR)</t>
+          <t>DAILIES TOTAL 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -539,12 +539,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PATANOL S</t>
+          <t>AIR OPTIX COLORS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PATANOL S</t>
+          <t>AIR OPTIX COLORS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -556,12 +556,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CLARIL</t>
+          <t>DACP TORIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CLARIL (ALC)</t>
+          <t>DACP TORIC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -573,12 +573,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PATADAY</t>
+          <t>DACP MF</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PATADAY (NVR)</t>
+          <t>DACP MF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -590,12 +590,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PATADAY</t>
+          <t>AIR OPTIX NIGHT &amp; DAY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PATADAY</t>
+          <t>AIR OPTIX NIGHT &amp; DAY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MAXIDEX</t>
+          <t>DACP SPHERE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAXIDEX (NOVARTIS)</t>
+          <t>DACP SPHERE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -624,12 +624,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MAXIDEX</t>
+          <t>OUTROS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MAXIDEX (ALC)</t>
+          <t>OUTROS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -641,12 +641,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TOBRADEX</t>
+          <t>AIR OPTIX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOBRADEX (ALC)</t>
+          <t>AIR OPTIX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -658,12 +658,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PRED FORTE</t>
+          <t>AIR OPTIX MULTIFOCAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PRED FORTE (ALC)</t>
+          <t>AIR OPTIX MULTIFOCAL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -675,12 +675,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TRAVATAN Z</t>
+          <t>AIR OPTIX TORIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TRAVATAN Z (ALC)</t>
+          <t>AIR OPTIX TORIC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -692,12 +692,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TRAVATAN Z</t>
+          <t>FRESHLOOK 1-DAY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TRAVATAN</t>
+          <t>FRESHLOOK 1-DAY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TOTAL 30</t>
+          <t>CLEAR CARE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TOTAL 30 (ALC)</t>
+          <t>CLEAR CARE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -726,12 +726,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DAILIES TOTAL1</t>
+          <t>CLENS 100</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DAILIES TOTAL1 (ALC)</t>
+          <t>CLENS 100</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DAILIES TOTAL1</t>
+          <t>OPTI FREE EXPRESS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DAILIES TOTAL ONE</t>
+          <t>OPTI FREE EXPRESS (ALC)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -758,28 +758,291 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OPTI FREE PUREMOIST KIT</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SYSTANE BALANCE</t>
+          <t>OPTI FREE PUREMOIS (ALC)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NAO</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OPTI FREE REPLENISH</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>REFRESH OPTIVE</t>
+          <t>OPTI FREE REPLENIS (ALC)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NAO</t>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CLARIL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CLARIL (ALC)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CLAROFT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CLAROFT (ALC)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LACRIMA PLUS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LACRIMA PLUS (ALC)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OFTANE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OFTANE (ALC)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SYSTANE LID WIPES</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SYSTANE LID WIPES (ALC)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SYSTANE UL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SYSTANE UL (ALC)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TRISORB</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TRISORB (ALC)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>VITALUX OMEGA 3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>VITALUX OMEGA 3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>OPTI FREE GOTAS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>OPTI FREE GOTAS</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SIMPLE CLEAN</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SIMPLE CLEAN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OPTI FREE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>OPTI FREE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>OPTILAR</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>OPTILAR</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ILUX PI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ILUX PI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ILUX EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ILUX EQUIPMENT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AZOPT</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AZOPT (NVR)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SIM</t>
         </is>
       </c>
     </row>
@@ -794,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,7 +1068,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Descrição</t>
+          <t>Descricao</t>
         </is>
       </c>
     </row>
@@ -817,7 +1080,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nome canônico do produto no sell-in (será o nome usado no dashboard)</t>
+          <t>Nome canonico do produto no sell-in (sera o nome usado no dashboard)</t>
         </is>
       </c>
     </row>
@@ -829,7 +1092,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nome do produto no sell-out (UM nome por linha)</t>
+          <t>Nome do produto no sell-out (UM nome por linha, lookup 1:1)</t>
         </is>
       </c>
     </row>
@@ -841,7 +1104,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM = mostra no dashboard. NAO = ignora (concorrentes, ruído)</t>
+          <t>SIM = mostra no dashboard. NAO = ignora (concorrentes, ruido)</t>
         </is>
       </c>
     </row>
@@ -861,7 +1124,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1. UMA LINHA POR PAR sell-in/sell-out</t>
+          <t>1. UMA LINHA POR PAR sell-in / sell-out (lookup 1:1 simples)</t>
         </is>
       </c>
     </row>
@@ -869,7 +1132,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2. Para mapear MULTIPLOS nomes do sell-out pro MESMO sell-in,</t>
+          <t>2. Cada PRODUTO_SELLOUT deve aparecer apenas UMA VEZ</t>
         </is>
       </c>
     </row>
@@ -877,7 +1140,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">   crie várias linhas com o mesmo PRODUTO_SELLIN</t>
+          <t>3. Match EXATO no nome (sem fuzzy, sem ;)</t>
         </is>
       </c>
     </row>
@@ -885,7 +1148,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3. Match EXATO no nome (sem fuzzy)</t>
+          <t>4. Se um sell-out aparecer 2x: mantem o primeiro, ignora os demais</t>
         </is>
       </c>
     </row>
@@ -893,139 +1156,75 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4. Produtos não listados aparecem em produtos_nao_mapeados.csv</t>
+          <t>5. CSV de duplicatas e gerado automaticamente para revisao</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6. Produtos nao listados aparecem em produtos_nao_mapeados.csv</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>EXEMPLO:</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Para o sell-in 'SYSTANE ULTRA' que aparece em 3 nomes diferentes no sell-out:</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PRODUTO_SELLIN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PRODUTO_SELLOUT</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PRODUTO_SELLIN</t>
+          <t>CLARIL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PRODUTO_SELLOUT</t>
+          <t>CLARIL (ALC)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SYSTANE ULTRA</t>
+          <t>AZOPT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SYSTANE UL</t>
+          <t>AZOPT (NVR)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SYSTANE ULTRA</t>
+          <t>SYSTANE UL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SYSTANE UL (SLC)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SYSTANE ULTRA</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SYSTANE U</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>↑ As 3 linhas vão somar no mesmo SYSTANE ULTRA do dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>FLUXO:</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1. Roda script Python</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2. Vê no console quais produtos faltam mapear</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3. Abre produtos_nao_mapeados.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>4. Copia pra esta planilha (1 linha por par)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>5. Roda Python de novo - dashboard 100% mapeado</t>
+          <t>SYSTANE UL (ALC)</t>
         </is>
       </c>
     </row>
